--- a/samples/board-model.xlsx
+++ b/samples/board-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nyank\Desktop\後藤さんのclaude\ai-builders-2026\gridlint\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABD2EC32-EB74-40A5-B94F-58819853EDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0133697-FBEB-4342-9357-12B571412CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD85FD4-8B53-4148-A504-8F02F8C3F08B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{86AB21AC-B89D-4E76-BF4C-FCBD29D48641}"/>
   </bookViews>
   <sheets>
     <sheet name="Operating Model" sheetId="2" r:id="rId1"/>
@@ -591,7 +591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1595F1A1-4311-46CA-B993-70FBDEFD32E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19148534-0FD6-43A0-AD26-5BA94623CED0}">
   <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1336,7 +1336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF106537-A219-4601-ABA8-4DBD0EB240B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD8BE7CA-DB84-4D0C-8F0A-B2D8E0467C30}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
